--- a/artfynd/A 38665-2025 artfynd.xlsx
+++ b/artfynd/A 38665-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102632160</v>
+        <v>102630573</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603755.1394039495</v>
+        <v>603585</v>
       </c>
       <c r="R2" t="n">
-        <v>7053972.866258857</v>
+        <v>7053971</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102630186</v>
+        <v>102630287</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603593.2478373433</v>
+        <v>603586</v>
       </c>
       <c r="R3" t="n">
-        <v>7054054.868231738</v>
+        <v>7054030</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,19 +842,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,37 +871,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102632166</v>
+        <v>102630633</v>
       </c>
       <c r="B4" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603755.1394039495</v>
+        <v>603585</v>
       </c>
       <c r="R4" t="n">
-        <v>7053972.866258857</v>
+        <v>7053968</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,19 +940,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +969,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102630789</v>
+        <v>102632620</v>
       </c>
       <c r="B5" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +980,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603691.8294285464</v>
+        <v>603747</v>
       </c>
       <c r="R5" t="n">
-        <v>7053985.938857629</v>
+        <v>7054058</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,19 +1038,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102630584</v>
+        <v>102632614</v>
       </c>
       <c r="B6" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603585.3022679708</v>
+        <v>603747</v>
       </c>
       <c r="R6" t="n">
-        <v>7053970.432762211</v>
+        <v>7054058</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1201,19 +1136,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102632614</v>
+        <v>102632433</v>
       </c>
       <c r="B7" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603746.9846984537</v>
+        <v>603749</v>
       </c>
       <c r="R7" t="n">
-        <v>7054058.55721344</v>
+        <v>7054000</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1314,19 +1234,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102630287</v>
+        <v>102630584</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603586.4591734014</v>
+        <v>603585</v>
       </c>
       <c r="R8" t="n">
-        <v>7054030.59645913</v>
+        <v>7053971</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1332,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1361,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102632433</v>
+        <v>102630789</v>
       </c>
       <c r="B9" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,21 +1372,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603748.8765702115</v>
+        <v>603692</v>
       </c>
       <c r="R9" t="n">
-        <v>7054000.72038187</v>
+        <v>7053986</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1540,19 +1430,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,15 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102630633</v>
+        <v>102630186</v>
       </c>
       <c r="B10" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1470,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603585.360387895</v>
+        <v>603593</v>
       </c>
       <c r="R10" t="n">
-        <v>7053968.653134489</v>
+        <v>7054054</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,19 +1528,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,15 +1557,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102632620</v>
+        <v>102632160</v>
       </c>
       <c r="B11" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,21 +1568,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1733,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603746.9846984537</v>
+        <v>603755</v>
       </c>
       <c r="R11" t="n">
-        <v>7054058.55721344</v>
+        <v>7053973</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1766,19 +1626,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,37 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102630573</v>
+        <v>102632166</v>
       </c>
       <c r="B12" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603585.3022679708</v>
+        <v>603755</v>
       </c>
       <c r="R12" t="n">
-        <v>7053970.432762211</v>
+        <v>7053973</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,19 +1724,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 38665-2025 artfynd.xlsx
+++ b/artfynd/A 38665-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102630573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102630287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102630633</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632620</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632614</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632433</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102630584</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102630789</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102630186</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632160</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1750,8 +1805,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632166</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>